--- a/Brandon-Carrillo-Valencia/Carrillo-Valencia_Ex3A_tables.xlsx
+++ b/Brandon-Carrillo-Valencia/Carrillo-Valencia_Ex3A_tables.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Brandon\Documents\DATA_Labs\W2_Workshop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Brandon\Documents\DATA_Labs\W2_Workshop\Brandon-Carrillo-Valencia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BC994C-5F5C-43BE-80AE-F6F898CB9744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989BC359-63DB-4191-98C9-1F777DA9C331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3975" yWindow="3300" windowWidth="22065" windowHeight="11520" activeTab="2" xr2:uid="{2EA6DB7B-6C81-4DE6-9705-67E076F4FFF2}"/>
+    <workbookView xWindow="9600" yWindow="3255" windowWidth="22065" windowHeight="11520" activeTab="2" xr2:uid="{2EA6DB7B-6C81-4DE6-9705-67E076F4FFF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Customer Info" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>CustomerID</t>
   </si>
@@ -80,6 +80,27 @@
   </si>
   <si>
     <t>Session Qty</t>
+  </si>
+  <si>
+    <t>Liz</t>
+  </si>
+  <si>
+    <t>123 Cool St, San Jose, CA</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>123-123-1234</t>
+  </si>
+  <si>
+    <t>Cupcake</t>
+  </si>
+  <si>
+    <t>Cane Corso</t>
+  </si>
+  <si>
+    <t>Black</t>
   </si>
 </sst>
 </file>
@@ -133,12 +154,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -474,11 +496,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F636B2E9-CDA8-4BF7-9EDB-285F8B020021}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
   </cols>
@@ -501,7 +523,21 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="3"/>
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -510,12 +546,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F79F59-E7CC-474F-B25C-B296CBD6B7EF}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -526,7 +563,7 @@
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D1" t="s">
@@ -534,6 +571,23 @@
       </c>
       <c r="E1" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -543,13 +597,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3FD4E2A-84EA-46B2-B1EF-49B7855AE48B}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -574,6 +628,26 @@
         <v>12</v>
       </c>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5">
+        <v>46127.4375</v>
+      </c>
+      <c r="E2">
+        <v>25</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
